--- a/annotazione/semantica/semantic_annotation_task.xlsx
+++ b/annotazione/semantica/semantic_annotation_task.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gretagorzoni/Desktop/Semantica2025/annotazione/semantica/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68838534-3C43-FB47-8EA0-82B46B1D2F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300D0791-4D36-8D4F-A1B7-48AE3F933E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -848,7 +848,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -932,6 +932,13 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -945,6 +952,13 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -975,20 +989,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1003,14 +1003,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{68D6B926-694B-6C43-93F7-12FEEE23B23D}" name="Tabella1" displayName="Tabella1" ref="A1:E101" totalsRowShown="0" headerRowDxfId="6" dataDxfId="0" headerRowBorderDxfId="7" tableBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{68D6B926-694B-6C43-93F7-12FEEE23B23D}" name="Tabella1" displayName="Tabella1" ref="A1:E101" totalsRowShown="0" headerRowDxfId="8" dataDxfId="6" headerRowBorderDxfId="7" tableBorderDxfId="5">
   <autoFilter ref="A1:E101" xr:uid="{68D6B926-694B-6C43-93F7-12FEEE23B23D}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{CAAA4359-FEFF-8848-A659-0FE5B437EA7A}" name="ID" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{FD52366E-01EA-CE46-96A3-F91BB5D80168}" name="contesto_precedente" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{E5B4346A-8109-B044-862F-28EA20532298}" name="CXN_NPN" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{65A43CF6-2576-7145-BD6A-3B93EB898C00}" name="contesto_successivo" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{ECC52311-FB0B-5840-9F12-51F1DB42D28B}" name="meaning" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{CAAA4359-FEFF-8848-A659-0FE5B437EA7A}" name="ID" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{FD52366E-01EA-CE46-96A3-F91BB5D80168}" name="contesto_precedente" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{E5B4346A-8109-B044-862F-28EA20532298}" name="CXN_NPN" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{65A43CF6-2576-7145-BD6A-3B93EB898C00}" name="contesto_successivo" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{ECC52311-FB0B-5840-9F12-51F1DB42D28B}" name="meaning" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/annotazione/semantica/semantic_annotation_task.xlsx
+++ b/annotazione/semantica/semantic_annotation_task.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gretagorzoni/Desktop/Semantica2025/annotazione/semantica/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300D0791-4D36-8D4F-A1B7-48AE3F933E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B118B13A-E626-544E-9981-C35AD3547B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
